--- a/DB_related/IPschemaTest_v1.xlsx
+++ b/DB_related/IPschemaTest_v1.xlsx
@@ -8,20 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peter\OneDrive\Documents\phecoding\dev-test1\test\DB_related\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2561C351-0F8E-426C-959C-9C9E072EF108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAA4945-E505-411D-9459-4F246FC4765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="7020" windowWidth="15105" windowHeight="6570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="device" sheetId="1" r:id="rId1"/>
+    <sheet name="IP_assignment" sheetId="1" r:id="rId1"/>
     <sheet name="schema" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
   <si>
     <t>pb1</t>
   </si>
@@ -44,9 +55,6 @@
     <t>core</t>
   </si>
   <si>
-    <t>device</t>
-  </si>
-  <si>
     <t>10.1.1.1</t>
   </si>
   <si>
@@ -78,6 +86,36 @@
   </si>
   <si>
     <t>SW_num</t>
+  </si>
+  <si>
+    <t>device_type</t>
+  </si>
+  <si>
+    <t>hostname</t>
+  </si>
+  <si>
+    <t>pb1_rt01</t>
+  </si>
+  <si>
+    <t>pb1_rt02</t>
+  </si>
+  <si>
+    <t>pb1_sw</t>
+  </si>
+  <si>
+    <t>pb2_rt01</t>
+  </si>
+  <si>
+    <t>pb2_rt02</t>
+  </si>
+  <si>
+    <t>pb2_core</t>
+  </si>
+  <si>
+    <t>pb2_sw1</t>
+  </si>
+  <si>
+    <t>pb2_sw2</t>
   </si>
 </sst>
 </file>
@@ -220,7 +258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -398,6 +436,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -561,8 +605,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -918,118 +963,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>3</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>3</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>3</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
       <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1065,16 +1189,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1082,16 +1206,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
